--- a/VR_Interactions_En.xlsx
+++ b/VR_Interactions_En.xlsx
@@ -12796,7 +12796,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82807794-1EE9-46DE-8DDE-903D0A149361}">
-  <dimension ref="A14:AH102"/>
+  <dimension ref="A14:AH103"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
@@ -14793,6 +14793,100 @@
         <v>6</v>
       </c>
     </row>
+    <row r="34" spans="1:34">
+      <c r="A34" s="21"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8">
+        <v>20</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="E34" s="8">
+        <v>22</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="I34" s="15">
+        <v>6</v>
+      </c>
+      <c r="J34" s="15">
+        <v>5</v>
+      </c>
+      <c r="K34" s="15">
+        <v>5</v>
+      </c>
+      <c r="L34" s="15">
+        <v>2</v>
+      </c>
+      <c r="M34" s="15">
+        <v>3</v>
+      </c>
+      <c r="N34" s="15">
+        <v>4</v>
+      </c>
+      <c r="O34" s="15">
+        <v>5</v>
+      </c>
+      <c r="P34" s="15">
+        <v>6</v>
+      </c>
+      <c r="Q34" s="15">
+        <v>2</v>
+      </c>
+      <c r="R34" s="15">
+        <v>5</v>
+      </c>
+      <c r="S34" s="15">
+        <v>3</v>
+      </c>
+      <c r="T34" s="15">
+        <v>3</v>
+      </c>
+      <c r="U34" s="15">
+        <v>5</v>
+      </c>
+      <c r="V34" s="15">
+        <v>5</v>
+      </c>
+      <c r="W34" s="15">
+        <v>3</v>
+      </c>
+      <c r="X34" s="15">
+        <v>4</v>
+      </c>
+      <c r="Y34" s="15">
+        <v>3</v>
+      </c>
+      <c r="Z34" s="15">
+        <v>4</v>
+      </c>
+      <c r="AA34" s="15">
+        <v>3</v>
+      </c>
+      <c r="AB34" s="15">
+        <v>6</v>
+      </c>
+      <c r="AC34" s="15">
+        <v>3</v>
+      </c>
+      <c r="AD34" s="15">
+        <v>6</v>
+      </c>
+      <c r="AE34" s="15">
+        <v>2</v>
+      </c>
+      <c r="AF34" s="15">
+        <v>3</v>
+      </c>
+      <c r="AG34" s="15">
+        <v>2</v>
+      </c>
+      <c r="AH34" s="15">
+        <v>4</v>
+      </c>
+    </row>
     <row r="37" spans="1:34">
       <c r="A37" s="18"/>
       <c r="B37" s="5"/>
@@ -16633,6 +16727,98 @@
         <v>5</v>
       </c>
     </row>
+    <row r="57" spans="1:34">
+      <c r="A57" s="21"/>
+      <c r="B57" s="8"/>
+      <c r="C57" s="8">
+        <v>20</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="E57" s="8">
+        <v>22</v>
+      </c>
+      <c r="F57" s="8"/>
+      <c r="I57" s="15">
+        <v>3</v>
+      </c>
+      <c r="J57" s="15">
+        <v>6</v>
+      </c>
+      <c r="K57" s="15">
+        <v>5</v>
+      </c>
+      <c r="L57" s="15">
+        <v>3</v>
+      </c>
+      <c r="M57" s="15">
+        <v>4</v>
+      </c>
+      <c r="N57" s="15">
+        <v>3</v>
+      </c>
+      <c r="O57" s="15">
+        <v>3</v>
+      </c>
+      <c r="P57" s="15">
+        <v>5</v>
+      </c>
+      <c r="Q57" s="15">
+        <v>3</v>
+      </c>
+      <c r="R57" s="15">
+        <v>5</v>
+      </c>
+      <c r="S57" s="15">
+        <v>5</v>
+      </c>
+      <c r="T57" s="15">
+        <v>4</v>
+      </c>
+      <c r="U57" s="15">
+        <v>5</v>
+      </c>
+      <c r="V57" s="15">
+        <v>3</v>
+      </c>
+      <c r="W57" s="15">
+        <v>3</v>
+      </c>
+      <c r="X57" s="15">
+        <v>3</v>
+      </c>
+      <c r="Y57" s="15">
+        <v>4</v>
+      </c>
+      <c r="Z57" s="15">
+        <v>5</v>
+      </c>
+      <c r="AA57" s="15">
+        <v>5</v>
+      </c>
+      <c r="AB57" s="15">
+        <v>3</v>
+      </c>
+      <c r="AC57" s="15">
+        <v>5</v>
+      </c>
+      <c r="AD57" s="15">
+        <v>3</v>
+      </c>
+      <c r="AE57" s="15">
+        <v>5</v>
+      </c>
+      <c r="AF57" s="15">
+        <v>5</v>
+      </c>
+      <c r="AG57" s="15">
+        <v>2</v>
+      </c>
+      <c r="AH57" s="15">
+        <v>4</v>
+      </c>
+    </row>
     <row r="60" spans="1:34">
       <c r="A60" s="18"/>
       <c r="B60" s="5"/>
@@ -18473,6 +18659,98 @@
         <v>7</v>
       </c>
     </row>
+    <row r="80" spans="1:34">
+      <c r="A80" s="21"/>
+      <c r="B80" s="8"/>
+      <c r="C80" s="8">
+        <v>20</v>
+      </c>
+      <c r="D80" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="E80" s="8">
+        <v>22</v>
+      </c>
+      <c r="F80" s="8"/>
+      <c r="I80" s="15">
+        <v>5</v>
+      </c>
+      <c r="J80" s="15">
+        <v>5</v>
+      </c>
+      <c r="K80" s="15">
+        <v>3</v>
+      </c>
+      <c r="L80" s="15">
+        <v>3</v>
+      </c>
+      <c r="M80" s="15">
+        <v>3</v>
+      </c>
+      <c r="N80" s="15">
+        <v>5</v>
+      </c>
+      <c r="O80" s="15">
+        <v>5</v>
+      </c>
+      <c r="P80" s="15">
+        <v>2</v>
+      </c>
+      <c r="Q80" s="15">
+        <v>4</v>
+      </c>
+      <c r="R80" s="15">
+        <v>3</v>
+      </c>
+      <c r="S80" s="15">
+        <v>5</v>
+      </c>
+      <c r="T80" s="15">
+        <v>5</v>
+      </c>
+      <c r="U80" s="15">
+        <v>6</v>
+      </c>
+      <c r="V80" s="15">
+        <v>4</v>
+      </c>
+      <c r="W80" s="15">
+        <v>5</v>
+      </c>
+      <c r="X80" s="15">
+        <v>3</v>
+      </c>
+      <c r="Y80" s="15">
+        <v>3</v>
+      </c>
+      <c r="Z80" s="15">
+        <v>5</v>
+      </c>
+      <c r="AA80" s="15">
+        <v>5</v>
+      </c>
+      <c r="AB80" s="15">
+        <v>3</v>
+      </c>
+      <c r="AC80" s="15">
+        <v>5</v>
+      </c>
+      <c r="AD80" s="15">
+        <v>3</v>
+      </c>
+      <c r="AE80" s="15">
+        <v>5</v>
+      </c>
+      <c r="AF80" s="15">
+        <v>3</v>
+      </c>
+      <c r="AG80" s="15">
+        <v>2</v>
+      </c>
+      <c r="AH80" s="15">
+        <v>5</v>
+      </c>
+    </row>
     <row r="83" spans="1:34">
       <c r="A83" s="18"/>
       <c r="B83" s="5"/>
@@ -20311,6 +20589,98 @@
       </c>
       <c r="AH102" s="17">
         <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:34">
+      <c r="A103" s="21"/>
+      <c r="B103" s="8"/>
+      <c r="C103" s="8">
+        <v>20</v>
+      </c>
+      <c r="D103" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="E103" s="8">
+        <v>22</v>
+      </c>
+      <c r="F103" s="8"/>
+      <c r="I103" s="15">
+        <v>6</v>
+      </c>
+      <c r="J103" s="15">
+        <v>6</v>
+      </c>
+      <c r="K103" s="15">
+        <v>2</v>
+      </c>
+      <c r="L103" s="15">
+        <v>3</v>
+      </c>
+      <c r="M103" s="15">
+        <v>3</v>
+      </c>
+      <c r="N103" s="15">
+        <v>5</v>
+      </c>
+      <c r="O103" s="15">
+        <v>5</v>
+      </c>
+      <c r="P103" s="15">
+        <v>5</v>
+      </c>
+      <c r="Q103" s="15">
+        <v>4</v>
+      </c>
+      <c r="R103" s="15">
+        <v>2</v>
+      </c>
+      <c r="S103" s="15">
+        <v>5</v>
+      </c>
+      <c r="T103" s="15">
+        <v>4</v>
+      </c>
+      <c r="U103" s="15">
+        <v>3</v>
+      </c>
+      <c r="V103" s="15">
+        <v>5</v>
+      </c>
+      <c r="W103" s="15">
+        <v>5</v>
+      </c>
+      <c r="X103" s="15">
+        <v>5</v>
+      </c>
+      <c r="Y103" s="15">
+        <v>4</v>
+      </c>
+      <c r="Z103" s="15">
+        <v>3</v>
+      </c>
+      <c r="AA103" s="15">
+        <v>3</v>
+      </c>
+      <c r="AB103" s="15">
+        <v>5</v>
+      </c>
+      <c r="AC103" s="15">
+        <v>3</v>
+      </c>
+      <c r="AD103" s="15">
+        <v>5</v>
+      </c>
+      <c r="AE103" s="15">
+        <v>3</v>
+      </c>
+      <c r="AF103" s="15">
+        <v>3</v>
+      </c>
+      <c r="AG103" s="15">
+        <v>2</v>
+      </c>
+      <c r="AH103" s="17">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/VR_Interactions_En.xlsx
+++ b/VR_Interactions_En.xlsx
@@ -6238,6 +6238,9 @@
       <c r="U9">
         <v>4</v>
       </c>
+      <c r="V9">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:71">
       <c r="A10" s="67"/>
@@ -6301,6 +6304,9 @@
       <c r="U10">
         <v>4</v>
       </c>
+      <c r="V10">
+        <v>2</v>
+      </c>
     </row>
     <row r="11" spans="1:71" ht="13.5">
       <c r="A11" s="66" t="s">
@@ -6365,6 +6371,9 @@
       </c>
       <c r="U11">
         <v>4</v>
+      </c>
+      <c r="V11">
+        <v>3</v>
       </c>
       <c r="BS11" s="22" t="s">
         <v>1</v>
@@ -6432,6 +6441,9 @@
       <c r="U12">
         <v>4</v>
       </c>
+      <c r="V12">
+        <v>2</v>
+      </c>
     </row>
     <row r="13" spans="1:71">
       <c r="A13" s="66" t="s">
@@ -6496,6 +6508,9 @@
       </c>
       <c r="U13">
         <v>4</v>
+      </c>
+      <c r="V13">
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:71">
@@ -6560,6 +6575,9 @@
       <c r="U14">
         <v>4</v>
       </c>
+      <c r="V14">
+        <v>2</v>
+      </c>
     </row>
     <row r="15" spans="1:71" ht="12.75" customHeight="1"/>
     <row r="16" spans="1:71" ht="18">
@@ -6567,7 +6585,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="12.75" customHeight="1">
+    <row r="17" spans="1:22" ht="12.75" customHeight="1">
       <c r="A17" s="92" t="s">
         <v>108</v>
       </c>
@@ -6631,8 +6649,11 @@
       <c r="U17">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:21" ht="12.75" customHeight="1">
+      <c r="V17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" ht="12.75" customHeight="1">
       <c r="A18" s="67"/>
       <c r="B18" t="s">
         <v>112</v>
@@ -6694,8 +6715,11 @@
       <c r="U18">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:21">
+      <c r="V18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" s="66" t="s">
         <v>109</v>
       </c>
@@ -6759,8 +6783,11 @@
       <c r="U19">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:21">
+      <c r="V19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="67"/>
       <c r="B20" t="s">
         <v>114</v>
@@ -6822,8 +6849,11 @@
       <c r="U20">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:21">
+      <c r="V20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="66" t="s">
         <v>110</v>
       </c>
@@ -6887,8 +6917,11 @@
       <c r="U21">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:21">
+      <c r="V21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22">
       <c r="A22" s="67"/>
       <c r="B22" t="s">
         <v>116</v>
@@ -6949,6 +6982,9 @@
       </c>
       <c r="U22">
         <v>3</v>
+      </c>
+      <c r="V22">
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:21" ht="12.75" customHeight="1"/>
@@ -6957,7 +6993,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="25" spans="1:21" ht="12.75" customHeight="1">
+    <row r="25" spans="1:22" ht="12.75" customHeight="1">
       <c r="A25" s="66" t="s">
         <v>108</v>
       </c>
@@ -7021,8 +7057,11 @@
       <c r="U25" s="8">
         <v>5</v>
       </c>
-    </row>
-    <row r="26" spans="1:21" ht="12.75" customHeight="1">
+      <c r="V25" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" ht="12.75" customHeight="1">
       <c r="A26" s="67"/>
       <c r="B26" s="5" t="s">
         <v>112</v>
@@ -7084,8 +7123,11 @@
       <c r="U26" s="8">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="1:21" ht="12.75" customHeight="1">
+      <c r="V26" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" ht="12.75" customHeight="1">
       <c r="A27" s="66" t="s">
         <v>109</v>
       </c>
@@ -7149,8 +7191,11 @@
       <c r="U27" s="8">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="1:21" ht="12.75" customHeight="1">
+      <c r="V27" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" ht="12.75" customHeight="1">
       <c r="A28" s="67"/>
       <c r="B28" s="5" t="s">
         <v>114</v>
@@ -7212,8 +7257,11 @@
       <c r="U28" s="8">
         <v>4</v>
       </c>
-    </row>
-    <row r="29" spans="1:21" ht="12.75" customHeight="1">
+      <c r="V28" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" ht="12.75" customHeight="1">
       <c r="A29" s="66" t="s">
         <v>110</v>
       </c>
@@ -7277,8 +7325,11 @@
       <c r="U29" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="30" spans="1:21" ht="12.75" customHeight="1">
+      <c r="V29" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" ht="12.75" customHeight="1">
       <c r="A30" s="67"/>
       <c r="B30" t="s">
         <v>116</v>
@@ -7340,6 +7391,9 @@
       <c r="U30" s="8">
         <v>3</v>
       </c>
+      <c r="V30" s="8">
+        <v>3</v>
+      </c>
     </row>
     <row r="32" spans="1:21" ht="18">
       <c r="A32" s="91" t="s">
@@ -7409,6 +7463,9 @@
       </c>
       <c r="U33" s="8">
         <v>5</v>
+      </c>
+      <c r="V33" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:22" ht="12.75" customHeight="1">
@@ -7473,6 +7530,9 @@
       <c r="U34" s="8">
         <v>4</v>
       </c>
+      <c r="V34" s="8">
+        <v>4</v>
+      </c>
     </row>
     <row r="35" spans="1:22" ht="12.75" customHeight="1">
       <c r="A35" s="66" t="s">
@@ -7537,6 +7597,9 @@
       </c>
       <c r="U35" s="8">
         <v>2</v>
+      </c>
+      <c r="V35" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:22" ht="12.75" customHeight="1">
@@ -7601,6 +7664,9 @@
       <c r="U36" s="8">
         <v>2</v>
       </c>
+      <c r="V36" s="8">
+        <v>5</v>
+      </c>
     </row>
     <row r="37" spans="1:22" ht="12.75" customHeight="1">
       <c r="A37" s="66" t="s">
@@ -7665,6 +7731,9 @@
       </c>
       <c r="U37" s="8">
         <v>3</v>
+      </c>
+      <c r="V37" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:22" ht="12.75" customHeight="1">
@@ -7728,6 +7797,9 @@
       </c>
       <c r="U38" s="8">
         <v>2</v>
+      </c>
+      <c r="V38" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:22" ht="12.75" customHeight="1"/>
@@ -9245,6 +9317,9 @@
       <c r="U9" s="4">
         <v>2</v>
       </c>
+      <c r="V9" s="4">
+        <v>4</v>
+      </c>
     </row>
     <row r="10" spans="1:71" ht="12.75" customHeight="1">
       <c r="A10" s="67"/>
@@ -9308,6 +9383,9 @@
       <c r="U10" s="4">
         <v>4</v>
       </c>
+      <c r="V10" s="4">
+        <v>4</v>
+      </c>
     </row>
     <row r="11" spans="1:71" ht="13.5" customHeight="1">
       <c r="A11" s="66" t="s">
@@ -9372,6 +9450,9 @@
       </c>
       <c r="U11" s="4">
         <v>2</v>
+      </c>
+      <c r="V11" s="4">
+        <v>5</v>
       </c>
       <c r="BS11" s="22" t="s">
         <v>1</v>
@@ -9439,6 +9520,9 @@
       <c r="U12" s="4">
         <v>4</v>
       </c>
+      <c r="V12" s="4">
+        <v>4</v>
+      </c>
     </row>
     <row r="13" spans="1:71" ht="12.75" customHeight="1">
       <c r="A13" s="66" t="s">
@@ -9503,6 +9587,9 @@
       </c>
       <c r="U13" s="4">
         <v>5</v>
+      </c>
+      <c r="V13" s="4">
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:71" ht="12.75" customHeight="1">
@@ -9567,6 +9654,9 @@
       <c r="U14" s="4">
         <v>5</v>
       </c>
+      <c r="V14" s="4">
+        <v>4</v>
+      </c>
     </row>
     <row r="15" spans="1:71" ht="12.75" customHeight="1"/>
     <row r="16" spans="1:71" ht="18">
@@ -9574,7 +9664,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="12.75" customHeight="1">
+    <row r="17" spans="1:22" ht="12.75" customHeight="1">
       <c r="A17" s="66" t="s">
         <v>108</v>
       </c>
@@ -9638,8 +9728,11 @@
       <c r="U17" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="1:21" ht="12.75" customHeight="1">
+      <c r="V17" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" ht="12.75" customHeight="1">
       <c r="A18" s="67"/>
       <c r="B18" s="5" t="s">
         <v>112</v>
@@ -9701,8 +9794,11 @@
       <c r="U18" s="8">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:21" ht="12.75" customHeight="1">
+      <c r="V18" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" ht="12.75" customHeight="1">
       <c r="A19" s="66" t="s">
         <v>109</v>
       </c>
@@ -9766,8 +9862,11 @@
       <c r="U19" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:21" ht="12.75" customHeight="1">
+      <c r="V19" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" ht="12.75" customHeight="1">
       <c r="A20" s="67"/>
       <c r="B20" s="5" t="s">
         <v>114</v>
@@ -9829,8 +9928,11 @@
       <c r="U20" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="21" spans="1:21" ht="12.75" customHeight="1">
+      <c r="V20" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" ht="12.75" customHeight="1">
       <c r="A21" s="66" t="s">
         <v>110</v>
       </c>
@@ -9894,8 +9996,11 @@
       <c r="U21" s="8">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:21" ht="12.75" customHeight="1">
+      <c r="V21" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" ht="12.75" customHeight="1">
       <c r="A22" s="67"/>
       <c r="B22" s="5" t="s">
         <v>116</v>
@@ -9955,6 +10060,9 @@
         <v>3</v>
       </c>
       <c r="U22" s="8">
+        <v>2</v>
+      </c>
+      <c r="V22" s="8">
         <v>2</v>
       </c>
     </row>
@@ -9964,7 +10072,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:21" ht="12.75" customHeight="1">
+    <row r="25" spans="1:22" ht="12.75" customHeight="1">
       <c r="A25" s="66" t="s">
         <v>108</v>
       </c>
@@ -10028,8 +10136,11 @@
       <c r="U25" s="8">
         <v>4</v>
       </c>
-    </row>
-    <row r="26" spans="1:21" ht="12.75" customHeight="1">
+      <c r="V25" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" ht="12.75" customHeight="1">
       <c r="A26" s="67"/>
       <c r="B26" s="5" t="s">
         <v>112</v>
@@ -10091,8 +10202,11 @@
       <c r="U26" s="8">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="1:21" ht="12.75" customHeight="1">
+      <c r="V26" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" ht="12.75" customHeight="1">
       <c r="A27" s="66" t="s">
         <v>109</v>
       </c>
@@ -10156,8 +10270,11 @@
       <c r="U27" s="8">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="1:21" ht="12.75" customHeight="1">
+      <c r="V27" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" ht="12.75" customHeight="1">
       <c r="A28" s="67"/>
       <c r="B28" s="5" t="s">
         <v>114</v>
@@ -10219,8 +10336,11 @@
       <c r="U28" s="8">
         <v>4</v>
       </c>
-    </row>
-    <row r="29" spans="1:21" ht="12.75" customHeight="1">
+      <c r="V28" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" ht="12.75" customHeight="1">
       <c r="A29" s="66" t="s">
         <v>110</v>
       </c>
@@ -10284,8 +10404,11 @@
       <c r="U29" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="30" spans="1:21" ht="12.75" customHeight="1">
+      <c r="V29" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" ht="12.75" customHeight="1">
       <c r="A30" s="67"/>
       <c r="B30" s="5" t="s">
         <v>116</v>
@@ -10346,6 +10469,9 @@
       </c>
       <c r="U30" s="8">
         <v>3</v>
+      </c>
+      <c r="V30" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:21" ht="12.75" customHeight="1"/>
@@ -10359,7 +10485,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:21" ht="18">
+    <row r="45" spans="1:22" ht="18">
       <c r="A45" s="94" t="s">
         <v>134</v>
       </c>
@@ -10423,8 +10549,11 @@
       <c r="U45" s="8" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="46" spans="1:21">
+      <c r="V45" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22">
       <c r="A46" s="66" t="s">
         <v>135</v>
       </c>
@@ -10488,8 +10617,11 @@
       <c r="U46" s="8" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="47" spans="1:21">
+      <c r="V46" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22">
       <c r="A47" s="67"/>
       <c r="B47" s="27" t="s">
         <v>128</v>
@@ -10551,8 +10683,11 @@
       <c r="U47" s="8" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="48" spans="1:21">
+      <c r="V47" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22">
       <c r="A48" s="66" t="s">
         <v>136</v>
       </c>
@@ -10616,8 +10751,11 @@
       <c r="U48" s="8" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="49" spans="1:21">
+      <c r="V48" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22">
       <c r="A49" s="67"/>
       <c r="B49" s="27" t="s">
         <v>130</v>
@@ -10679,8 +10817,11 @@
       <c r="U49" s="8" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="50" spans="1:21">
+      <c r="V49" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22">
       <c r="A50" s="66" t="s">
         <v>137</v>
       </c>
@@ -10744,8 +10885,11 @@
       <c r="U50" s="15" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="51" spans="1:21">
+      <c r="V50" s="15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22">
       <c r="A51" s="67"/>
       <c r="B51" s="28" t="s">
         <v>132</v>
@@ -10805,6 +10949,9 @@
         <v>17</v>
       </c>
       <c r="U51" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="V51" s="15" t="s">
         <v>17</v>
       </c>
     </row>
@@ -10951,6 +11098,9 @@
       <c r="U9" s="12">
         <v>4</v>
       </c>
+      <c r="V9" s="12">
+        <v>5</v>
+      </c>
     </row>
     <row r="10" spans="1:60" ht="12.75" customHeight="1">
       <c r="A10" s="67"/>
@@ -11014,6 +11164,9 @@
       <c r="U10" s="12">
         <v>4</v>
       </c>
+      <c r="V10" s="12">
+        <v>4</v>
+      </c>
     </row>
     <row r="11" spans="1:60" ht="12.75" customHeight="1">
       <c r="A11" s="66" t="s">
@@ -11078,6 +11231,9 @@
       </c>
       <c r="U11" s="12">
         <v>3</v>
+      </c>
+      <c r="V11" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:60" ht="12.75" customHeight="1">
@@ -11142,6 +11298,9 @@
       <c r="U12" s="12">
         <v>4</v>
       </c>
+      <c r="V12" s="12">
+        <v>4</v>
+      </c>
     </row>
     <row r="13" spans="1:60" ht="12.75" customHeight="1">
       <c r="A13" s="66" t="s">
@@ -11205,6 +11364,9 @@
         <v>4</v>
       </c>
       <c r="U13" s="12">
+        <v>4</v>
+      </c>
+      <c r="V13" s="12">
         <v>4</v>
       </c>
     </row>
@@ -11270,6 +11432,9 @@
       <c r="U14" s="12">
         <v>4</v>
       </c>
+      <c r="V14" s="12">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:60" ht="13.5">
       <c r="BH15" s="22" t="s">
@@ -11281,7 +11446,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="12.75" customHeight="1">
+    <row r="17" spans="1:22" ht="12.75" customHeight="1">
       <c r="A17" s="66" t="s">
         <v>108</v>
       </c>
@@ -11345,8 +11510,11 @@
       <c r="U17" s="15">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:21" ht="12.75" customHeight="1">
+      <c r="V17" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" ht="12.75" customHeight="1">
       <c r="A18" s="67"/>
       <c r="B18" s="13" t="s">
         <v>112</v>
@@ -11408,8 +11576,11 @@
       <c r="U18" s="15">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:21" ht="12.75" customHeight="1">
+      <c r="V18" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" ht="12.75" customHeight="1">
       <c r="A19" s="66" t="s">
         <v>109</v>
       </c>
@@ -11473,8 +11644,11 @@
       <c r="U19" s="15">
         <v>2</v>
       </c>
-    </row>
-    <row r="20" spans="1:21" ht="12.75" customHeight="1">
+      <c r="V19" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" ht="12.75" customHeight="1">
       <c r="A20" s="67"/>
       <c r="B20" s="13" t="s">
         <v>114</v>
@@ -11536,8 +11710,11 @@
       <c r="U20" s="15">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:21" ht="12.75" customHeight="1">
+      <c r="V20" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" ht="12.75" customHeight="1">
       <c r="A21" s="66" t="s">
         <v>110</v>
       </c>
@@ -11601,8 +11778,11 @@
       <c r="U21" s="15">
         <v>2</v>
       </c>
-    </row>
-    <row r="22" spans="1:21" ht="12.75" customHeight="1">
+      <c r="V21" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" ht="12.75" customHeight="1">
       <c r="A22" s="67"/>
       <c r="B22" t="s">
         <v>116</v>
@@ -11664,13 +11844,16 @@
       <c r="U22" s="15">
         <v>2</v>
       </c>
+      <c r="V22" s="15">
+        <v>4</v>
+      </c>
     </row>
     <row r="24" spans="1:21" ht="18">
       <c r="A24" s="31" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:21" ht="12.75" customHeight="1">
+    <row r="25" spans="1:22" ht="12.75" customHeight="1">
       <c r="A25" s="66" t="s">
         <v>108</v>
       </c>
@@ -11734,8 +11917,11 @@
       <c r="U25" s="15">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:21" ht="12.75" customHeight="1">
+      <c r="V25" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" ht="12.75" customHeight="1">
       <c r="A26" s="67"/>
       <c r="B26" s="13" t="s">
         <v>112</v>
@@ -11797,8 +11983,11 @@
       <c r="U26" s="15">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="1:21" ht="12.75" customHeight="1">
+      <c r="V26" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" ht="12.75" customHeight="1">
       <c r="A27" s="66" t="s">
         <v>109</v>
       </c>
@@ -11862,8 +12051,11 @@
       <c r="U27" s="15">
         <v>2</v>
       </c>
-    </row>
-    <row r="28" spans="1:21" ht="12.75" customHeight="1">
+      <c r="V27" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" ht="12.75" customHeight="1">
       <c r="A28" s="67"/>
       <c r="B28" s="13" t="s">
         <v>114</v>
@@ -11925,8 +12117,11 @@
       <c r="U28" s="15">
         <v>4</v>
       </c>
-    </row>
-    <row r="29" spans="1:21" ht="12.75" customHeight="1">
+      <c r="V28" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" ht="12.75" customHeight="1">
       <c r="A29" s="66" t="s">
         <v>110</v>
       </c>
@@ -11990,8 +12185,11 @@
       <c r="U29" s="15">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="1:21" ht="12.75" customHeight="1">
+      <c r="V29" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" ht="12.75" customHeight="1">
       <c r="A30" s="67"/>
       <c r="B30" t="s">
         <v>116</v>
@@ -12053,13 +12251,16 @@
       <c r="U30" s="15">
         <v>3</v>
       </c>
+      <c r="V30" s="15">
+        <v>4</v>
+      </c>
     </row>
     <row r="32" spans="1:21" ht="18">
       <c r="A32" s="31" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:21" ht="12.75" customHeight="1">
+    <row r="33" spans="1:22" ht="12.75" customHeight="1">
       <c r="A33" s="66" t="s">
         <v>108</v>
       </c>
@@ -12123,8 +12324,11 @@
       <c r="U33" s="15">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="1:21" ht="12.75" customHeight="1">
+      <c r="V33" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" ht="12.75" customHeight="1">
       <c r="A34" s="67"/>
       <c r="B34" s="13" t="s">
         <v>112</v>
@@ -12186,8 +12390,11 @@
       <c r="U34" s="15">
         <v>4</v>
       </c>
-    </row>
-    <row r="35" spans="1:21" ht="12.75" customHeight="1">
+      <c r="V34" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" ht="12.75" customHeight="1">
       <c r="A35" s="66" t="s">
         <v>109</v>
       </c>
@@ -12251,8 +12458,11 @@
       <c r="U35" s="15">
         <v>4</v>
       </c>
-    </row>
-    <row r="36" spans="1:21" ht="12.75" customHeight="1">
+      <c r="V35" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" ht="12.75" customHeight="1">
       <c r="A36" s="67"/>
       <c r="B36" s="13" t="s">
         <v>114</v>
@@ -12314,8 +12524,11 @@
       <c r="U36" s="15">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="1:21" ht="12.75" customHeight="1">
+      <c r="V36" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" ht="12.75" customHeight="1">
       <c r="A37" s="66" t="s">
         <v>110</v>
       </c>
@@ -12379,8 +12592,11 @@
       <c r="U37" s="15">
         <v>2</v>
       </c>
-    </row>
-    <row r="38" spans="1:21" ht="12.75" customHeight="1">
+      <c r="V37" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" ht="12.75" customHeight="1">
       <c r="A38" s="67"/>
       <c r="B38" t="s">
         <v>116</v>
@@ -12442,13 +12658,16 @@
       <c r="U38" s="15">
         <v>2</v>
       </c>
+      <c r="V38" s="15">
+        <v>4</v>
+      </c>
     </row>
     <row r="44" spans="1:21" ht="20.25">
       <c r="A44" s="34" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:21" ht="20.25">
+    <row r="45" spans="1:22" ht="20.25">
       <c r="A45" s="29" t="s">
         <v>134</v>
       </c>
@@ -12512,8 +12731,11 @@
       <c r="U45" s="15" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="46" spans="1:21" ht="18">
+      <c r="V45" s="15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" ht="18">
       <c r="A46" s="94" t="s">
         <v>135</v>
       </c>
@@ -12577,8 +12799,11 @@
       <c r="U46" s="15" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="47" spans="1:21" ht="18">
+      <c r="V46" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" ht="18">
       <c r="A47" s="25" t="s">
         <v>136</v>
       </c>
@@ -12642,8 +12867,11 @@
       <c r="U47" s="15" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="48" spans="1:21">
+      <c r="V47" s="15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22">
       <c r="A48" s="71" t="s">
         <v>137</v>
       </c>
@@ -12707,8 +12935,11 @@
       <c r="U48" s="15" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="49" spans="1:21">
+      <c r="V48" s="15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22">
       <c r="A49" s="71"/>
       <c r="B49" t="s">
         <v>143</v>
@@ -12769,6 +13000,9 @@
       </c>
       <c r="U49" s="15" t="s">
         <v>19</v>
+      </c>
+      <c r="V49" s="15" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -14794,8 +15028,14 @@
       </c>
     </row>
     <row r="34" spans="1:34">
-      <c r="A34" s="21"/>
-      <c r="B34" s="8"/>
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>6-30-2025 18:10:25</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>155</v>
+      </c>
       <c r="C34" s="8">
         <v>20</v>
       </c>
